--- a/Resources/InvoiceASAP_Template_2025.xlsx
+++ b/Resources/InvoiceASAP_Template_2025.xlsx
@@ -1689,7 +1689,7 @@
         <v>7</v>
       </c>
       <c r="H70" s="11">
-        <f>SUMIF(G9:G67, "X", H9:H69)*H69</f>
+        <f>SUMIF(G8:G67, "X", H8:H67)*H69</f>
         <v>0</v>
       </c>
       <c r="J70" s="1"/>
